--- a/Config/Excel/panel.xlsx
+++ b/Config/Excel/panel.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
   <si>
     <t>id</t>
   </si>
@@ -65,6 +65,24 @@
   </si>
   <si>
     <t>测试界面2</t>
+  </si>
+  <si>
+    <t>Assets/Bundles/UI/Panel/Login/LoginPanel</t>
+  </si>
+  <si>
+    <t>登录界面</t>
+  </si>
+  <si>
+    <t>Assets/Bundles/UI/Panel/Package/PackagePanel</t>
+  </si>
+  <si>
+    <t>背包界面</t>
+  </si>
+  <si>
+    <t>Assets/Bundles/UI/Panel/Overview/OverviewPanel</t>
+  </si>
+  <si>
+    <t>总览界面</t>
   </si>
 </sst>
 </file>
@@ -1032,8 +1050,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="2"/>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="54.75" customWidth="1"/>
     <col min="3" max="3" width="27.875" customWidth="1"/>
@@ -1100,6 +1118,39 @@
       </c>
       <c r="C6" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7">
+        <v>1001</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8">
+        <v>1002</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9">
+        <v>1003</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Excel/panel.xlsx
+++ b/Config/Excel/panel.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
   <si>
     <t>id</t>
   </si>
@@ -83,6 +83,12 @@
   </si>
   <si>
     <t>总览界面</t>
+  </si>
+  <si>
+    <t>Assets/Bundles/UI/Panel/Battle/BattleBgPanel</t>
+  </si>
+  <si>
+    <t>战斗底板</t>
   </si>
 </sst>
 </file>
@@ -1050,7 +1056,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="54.75" customWidth="1"/>
@@ -1151,6 +1157,47 @@
       </c>
       <c r="C9" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10">
+        <v>1004</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16">
+        <v>1010</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Excel/panel.xlsx
+++ b/Config/Excel/panel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProjects\Project001\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{007D97F8-9698-4CD2-B789-CE4130DC5502}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72CB4F38-BE2E-47B2-925D-9BFEF6F62C39}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="27945" windowHeight="12255" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="15">
   <si>
     <t>id</t>
   </si>
@@ -65,6 +65,10 @@
   </si>
   <si>
     <t>Assets/Bundles/UI/Prefabs/Panel/GMPanel</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Bundles/UI/Prefabs/Panel/Overview/OverviewPanel</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -395,10 +399,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="2" max="2" width="50.25" customWidth="1"/>
+    <col min="2" max="2" width="66.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.15">
@@ -507,6 +511,32 @@
       </c>
       <c r="C9">
         <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A10">
+        <v>1004</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A11">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A12">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A13">
+        <v>1007</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Excel/panel.xlsx
+++ b/Config/Excel/panel.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20379"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProjects\Project001\Config\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72CB4F38-BE2E-47B2-925D-9BFEF6F62C39}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="27945" windowHeight="12255" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,11 +12,24 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
   <si>
     <t>id</t>
   </si>
@@ -61,22 +68,28 @@
   </si>
   <si>
     <t>Assets/Bundles/UI/Prefabs/Panel/LoadingPanel</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Assets/Bundles/UI/Prefabs/Panel/GMPanel</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Assets/Bundles/UI/Prefabs/Panel/Overview/OverviewPanel</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Bundles/UI/Prefabs/Panel/Backpack/BackpackPanel</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -88,27 +101,349 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -116,9 +451,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -133,17 +710,61 @@
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -393,19 +1014,19 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:F13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="2" width="66.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -416,7 +1037,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -430,7 +1051,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -444,7 +1065,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -455,7 +1076,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>1</v>
       </c>
@@ -467,7 +1088,7 @@
       </c>
       <c r="F5" s="1"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>2</v>
       </c>
@@ -479,7 +1100,7 @@
       </c>
       <c r="F6" s="1"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>1001</v>
       </c>
@@ -491,7 +1112,7 @@
       </c>
       <c r="F7" s="1"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:3">
       <c r="A8">
         <v>1002</v>
       </c>
@@ -502,7 +1123,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:3">
       <c r="A9">
         <v>1003</v>
       </c>
@@ -513,7 +1134,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:3">
       <c r="A10">
         <v>1004</v>
       </c>
@@ -524,46 +1145,54 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:3">
       <c r="A11">
         <v>1005</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
       <c r="A12">
         <v>1006</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:1">
       <c r="A13">
         <v>1007</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Config/Excel/panel.xlsx
+++ b/Config/Excel/panel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProjects\Project001\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB2A0BB2-024F-40B6-8EEC-649BC8870015}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF537E72-BD2C-48F0-82DF-E63204ECA29F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="27945" windowHeight="12255" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,12 +51,6 @@
     <t>备注</t>
   </si>
   <si>
-    <t>Assets/Bundles/UI/Prefabs/Panel/TestGroup1</t>
-  </si>
-  <si>
-    <t>Assets/Bundles/UI/Prefabs/Panel/TestGroup2</t>
-  </si>
-  <si>
     <t>Assets/Bundles/UI/Prefabs/Panel/LoginPanel</t>
   </si>
   <si>
@@ -78,6 +72,14 @@
   </si>
   <si>
     <t>Battle_Units_Group占位</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Bundles/UI/Prefabs/Panel/TestPanel1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Bundles/UI/Prefabs/Panel/TestPanel2</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -469,8 +471,8 @@
       <c r="A5">
         <v>1</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>9</v>
+      <c r="B5" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -481,8 +483,8 @@
       <c r="A6">
         <v>2</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>10</v>
+      <c r="B6" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -494,7 +496,7 @@
         <v>1001</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C7">
         <v>2</v>
@@ -506,7 +508,7 @@
         <v>1002</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C8">
         <v>3</v>
@@ -517,7 +519,7 @@
         <v>1003</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -528,7 +530,7 @@
         <v>1004</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C10">
         <v>2</v>
@@ -539,7 +541,7 @@
         <v>1005</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C11">
         <v>2</v>
@@ -551,7 +553,7 @@
       </c>
       <c r="B12" s="2"/>
       <c r="D12" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.15">
@@ -559,7 +561,7 @@
         <v>1007</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C13">
         <v>3</v>

--- a/Config/Excel/panel.xlsx
+++ b/Config/Excel/panel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProjects\Project001\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF537E72-BD2C-48F0-82DF-E63204ECA29F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF16A327-FF4C-4489-BC5B-F3EFE0208313}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="27945" windowHeight="12255" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="20">
   <si>
     <t>id</t>
   </si>
@@ -80,6 +80,14 @@
   </si>
   <si>
     <t>Assets/Bundles/UI/Prefabs/Panel/TestPanel2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Bundles/UI/Prefabs/Panel/Battle/BattleActionPanel</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Bundles/UI/Prefabs/Panel/Battle/BattleActionPanel2</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -410,7 +418,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="2" width="66.125" customWidth="1"/>
@@ -565,6 +573,73 @@
       </c>
       <c r="C13">
         <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A14">
+        <v>1008</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A15">
+        <v>1009</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A16">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A17">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A18">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A19">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A20">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A21">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A22">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A23">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A24">
+        <v>1018</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Excel/panel.xlsx
+++ b/Config/Excel/panel.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20379"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProjects\Project001\Config\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF537E72-BD2C-48F0-82DF-E63204ECA29F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="27945" windowHeight="12255" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="30720" windowHeight="13380"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,11 +12,24 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
   <si>
     <t>id</t>
   </si>
@@ -51,6 +58,18 @@
     <t>备注</t>
   </si>
   <si>
+    <t>Assets/Bundles/UI/Prefabs/Panel/TestPanel1</t>
+  </si>
+  <si>
+    <t>Assets/Bundles/UI/Prefabs/Panel/TestPanel2</t>
+  </si>
+  <si>
+    <t>Assets/Bundles/UI/Prefabs/Panel/Battle/BattleFormation</t>
+  </si>
+  <si>
+    <t>BattleFormation</t>
+  </si>
+  <si>
     <t>Assets/Bundles/UI/Prefabs/Panel/LoginPanel</t>
   </si>
   <si>
@@ -64,30 +83,22 @@
   </si>
   <si>
     <t>Assets/Bundles/UI/Prefabs/Panel/Backpack/BackpackPanel</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Assets/Bundles/UI/Prefabs/Panel/BattleLoadingPanel</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Battle_Units_Group占位</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Bundles/UI/Prefabs/Panel/TestPanel1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Bundles/UI/Prefabs/Panel/TestPanel2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -99,27 +110,349 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -127,9 +460,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -137,24 +712,68 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -404,20 +1023,20 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:F13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
-    <col min="2" max="2" width="66.125" customWidth="1"/>
+    <col min="2" max="2" width="66.1296296296296" customWidth="1"/>
     <col min="4" max="4" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -428,7 +1047,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -442,7 +1061,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -456,7 +1075,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -467,131 +1086,138 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>1</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>16</v>
+      <c r="B5" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
-      <c r="F5" s="1"/>
+      <c r="F5" s="2"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>2</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>17</v>
+      <c r="B6" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
-      <c r="F6" s="1"/>
+      <c r="F6" s="2"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:6">
       <c r="A7">
+        <v>9001</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7">
+        <v>99</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8">
         <v>1001</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7">
+      <c r="B8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8">
         <v>2</v>
       </c>
-      <c r="F7" s="1"/>
+      <c r="F8" s="2"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A8">
+    <row r="9" spans="1:6">
+      <c r="A9">
         <v>1002</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8">
+      <c r="B9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A9">
+    <row r="10" spans="1:6">
+      <c r="A10">
         <v>1003</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A10">
-        <v>1004</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>12</v>
+      <c r="B10" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="C10">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:6">
       <c r="A11">
-        <v>1005</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>13</v>
+        <v>1004</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="C11">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:6">
       <c r="A12">
-        <v>1006</v>
-      </c>
-      <c r="B12" s="2"/>
-      <c r="D12" s="2" t="s">
-        <v>15</v>
+        <v>1005</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:6">
       <c r="A13">
         <v>1007</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>14</v>
+      <c r="B13" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="C13">
         <v>3</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>